--- a/ConfigWorkspace/Data/enemy_drop.xlsx
+++ b/ConfigWorkspace/Data/enemy_drop.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="T:\GAMES\deepseaoil\ConfigWorkspace\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2F77CEB-462B-4481-A1F4-618F00356CB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F29E1951-B34D-4D72-ADF5-17421512D375}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2085" yWindow="4125" windowWidth="19785" windowHeight="15525" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2730" yWindow="2730" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/ConfigWorkspace/Data/enemy_drop.xlsx
+++ b/ConfigWorkspace/Data/enemy_drop.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="T:\GAMES\deepseaoil\ConfigWorkspace\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2F77CEB-462B-4481-A1F4-618F00356CB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1406F820-6ACC-4CFC-805B-90B2E2C9FD8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2085" yWindow="4125" windowWidth="19785" windowHeight="15525" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4095" yWindow="5055" windowWidth="26760" windowHeight="13965" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -545,7 +545,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="2" width="8.875" style="1"/>
@@ -705,10 +705,20 @@
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="E9" s="1"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="1"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.15">
       <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/ConfigWorkspace/Data/enemy_drop.xlsx
+++ b/ConfigWorkspace/Data/enemy_drop.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="T:\GAMES\deepseaoil\ConfigWorkspace\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1406F820-6ACC-4CFC-805B-90B2E2C9FD8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F29E1951-B34D-4D72-ADF5-17421512D375}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4095" yWindow="5055" windowWidth="26760" windowHeight="13965" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2730" yWindow="2730" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -545,7 +545,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="2" width="8.875" style="1"/>
@@ -705,20 +705,10 @@
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="E9" s="2"/>
-      <c r="F9" s="1"/>
+      <c r="E9" s="1"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.15">
       <c r="E10" s="1"/>
-      <c r="F10" s="1"/>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="E12" s="1"/>
-      <c r="F12" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
